--- a/dokumen/Template Master (IT) FIX.xlsx
+++ b/dokumen/Template Master (IT) FIX.xlsx
@@ -3245,7 +3245,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
+  <sheetPr filterMode="true">
     <tabColor rgb="FF34B3FB"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
@@ -4003,7 +4003,7 @@
       </c>
       <c r="BB18" s="51"/>
     </row>
-    <row r="19" s="60" customFormat="true" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" s="60" customFormat="true" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="53" t="n">
         <v>1</v>
       </c>
@@ -4113,7 +4113,7 @@
       <c r="BA19" s="62"/>
       <c r="BB19" s="62"/>
     </row>
-    <row r="20" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="53"/>
       <c r="B20" s="53"/>
       <c r="C20" s="54" t="n">
@@ -4187,7 +4187,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="53"/>
       <c r="B21" s="53"/>
       <c r="C21" s="54" t="n">
@@ -4261,7 +4261,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="53"/>
       <c r="B22" s="53"/>
       <c r="C22" s="54" t="n">
@@ -4337,7 +4337,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="53"/>
       <c r="B23" s="53"/>
       <c r="C23" s="54" t="n">
@@ -4412,7 +4412,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="53"/>
       <c r="B24" s="53"/>
       <c r="C24" s="54" t="n">
@@ -4636,7 +4636,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="53"/>
       <c r="B27" s="53"/>
       <c r="C27" s="54" t="n">
@@ -4711,7 +4711,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="53"/>
       <c r="B28" s="53"/>
       <c r="C28" s="54" t="n">
@@ -4785,7 +4785,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="53"/>
       <c r="B29" s="53"/>
       <c r="C29" s="54" t="n">
@@ -4860,7 +4860,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="53"/>
       <c r="B30" s="53"/>
       <c r="C30" s="54" t="n">
@@ -4934,7 +4934,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="53"/>
       <c r="B31" s="53"/>
       <c r="C31" s="54" t="n">
@@ -5008,7 +5008,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="53"/>
       <c r="B32" s="53"/>
       <c r="C32" s="54" t="n">
@@ -5082,7 +5082,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="53"/>
       <c r="B33" s="53"/>
       <c r="C33" s="54" t="n">
@@ -5156,7 +5156,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="53"/>
       <c r="B34" s="53"/>
       <c r="C34" s="54" t="n">
@@ -5230,7 +5230,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="53"/>
       <c r="B35" s="53"/>
       <c r="C35" s="54" t="n">
@@ -5304,7 +5304,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="53"/>
       <c r="B36" s="53"/>
       <c r="C36" s="54" t="n">
@@ -5378,7 +5378,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="53"/>
       <c r="B37" s="53"/>
       <c r="C37" s="54" t="n">
@@ -5452,7 +5452,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="53"/>
       <c r="B38" s="53"/>
       <c r="C38" s="54" t="n">
@@ -5526,7 +5526,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="53"/>
       <c r="B39" s="53"/>
       <c r="C39" s="54" t="n">
@@ -5600,7 +5600,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="53"/>
       <c r="B40" s="53"/>
       <c r="C40" s="54" t="n">
@@ -5674,7 +5674,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="53"/>
       <c r="B41" s="53"/>
       <c r="C41" s="63" t="n">
@@ -5746,7 +5746,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="53"/>
       <c r="B42" s="53"/>
       <c r="C42" s="63" t="n">
@@ -5811,7 +5811,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="53"/>
       <c r="B43" s="53"/>
       <c r="C43" s="63" t="n">
@@ -5885,7 +5885,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="53"/>
       <c r="B44" s="53"/>
       <c r="C44" s="63" t="n">
@@ -5956,7 +5956,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="53"/>
       <c r="B45" s="53"/>
       <c r="C45" s="68" t="n">
@@ -6032,7 +6032,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="53"/>
       <c r="B46" s="53"/>
       <c r="C46" s="68" t="n">
@@ -6106,7 +6106,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="53"/>
       <c r="B47" s="53"/>
       <c r="C47" s="68" t="n">
@@ -6181,7 +6181,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="53"/>
       <c r="B48" s="53"/>
       <c r="C48" s="68" t="n">
@@ -6256,7 +6256,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="53"/>
       <c r="B49" s="53"/>
       <c r="C49" s="68" t="n">
@@ -6330,7 +6330,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="53"/>
       <c r="B50" s="53"/>
       <c r="C50" s="68" t="n">
@@ -6405,7 +6405,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="53"/>
       <c r="B51" s="53"/>
       <c r="C51" s="68" t="n">
@@ -6480,7 +6480,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="53"/>
       <c r="B52" s="53"/>
       <c r="C52" s="68" t="n">
@@ -6554,7 +6554,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="53"/>
       <c r="B53" s="53"/>
       <c r="C53" s="68" t="n">
@@ -6629,7 +6629,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="53"/>
       <c r="B54" s="53"/>
       <c r="C54" s="68" t="n">
@@ -6704,7 +6704,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="53"/>
       <c r="B55" s="53"/>
       <c r="C55" s="68" t="n">
@@ -6778,7 +6778,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="53"/>
       <c r="B56" s="53"/>
       <c r="C56" s="68" t="n">
@@ -6853,7 +6853,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="53"/>
       <c r="B57" s="53"/>
       <c r="C57" s="68" t="n">
@@ -6928,7 +6928,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="53"/>
       <c r="B58" s="53"/>
       <c r="C58" s="68" t="n">
@@ -7002,7 +7002,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="53"/>
       <c r="B59" s="53"/>
       <c r="C59" s="68" t="n">
@@ -7077,7 +7077,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="53"/>
       <c r="B60" s="53"/>
       <c r="C60" s="68" t="n">
@@ -7152,7 +7152,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="53"/>
       <c r="B61" s="53"/>
       <c r="C61" s="68" t="n">
@@ -7226,7 +7226,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="53"/>
       <c r="B62" s="53"/>
       <c r="C62" s="68" t="n">
@@ -7301,7 +7301,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="53"/>
       <c r="B63" s="53"/>
       <c r="C63" s="68" t="n">
@@ -7377,7 +7377,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="53"/>
       <c r="B64" s="53"/>
       <c r="C64" s="68" t="n">
@@ -7451,7 +7451,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="53"/>
       <c r="B65" s="53"/>
       <c r="C65" s="68" t="n">
@@ -7526,7 +7526,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="53"/>
       <c r="B66" s="53"/>
       <c r="C66" s="68" t="n">
@@ -7602,7 +7602,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="53"/>
       <c r="B67" s="53"/>
       <c r="C67" s="68" t="n">
@@ -7676,7 +7676,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="53"/>
       <c r="B68" s="53"/>
       <c r="C68" s="68" t="n">
@@ -7751,7 +7751,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="53"/>
       <c r="B69" s="53"/>
       <c r="C69" s="68" t="n">
@@ -7827,7 +7827,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="53"/>
       <c r="B70" s="53"/>
       <c r="C70" s="68" t="n">
@@ -7902,7 +7902,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="53"/>
       <c r="B71" s="53"/>
       <c r="C71" s="68" t="n">
@@ -7977,7 +7977,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="53"/>
       <c r="B72" s="53"/>
       <c r="C72" s="68" t="n">
@@ -8053,7 +8053,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="53"/>
       <c r="B73" s="53"/>
       <c r="C73" s="68" t="n">
@@ -8128,7 +8128,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="53"/>
       <c r="B74" s="53"/>
       <c r="C74" s="68" t="n">
@@ -8203,7 +8203,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="53"/>
       <c r="B75" s="53"/>
       <c r="C75" s="68" t="n">
@@ -8279,7 +8279,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="53"/>
       <c r="B76" s="53"/>
       <c r="C76" s="68" t="n">
@@ -8354,7 +8354,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="53"/>
       <c r="B77" s="53"/>
       <c r="C77" s="68" t="n">
@@ -8429,7 +8429,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="53"/>
       <c r="B78" s="53"/>
       <c r="C78" s="68" t="n">
@@ -8505,7 +8505,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="53"/>
       <c r="B79" s="53"/>
       <c r="C79" s="68" t="n">
@@ -8580,7 +8580,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="53"/>
       <c r="B80" s="53"/>
       <c r="C80" s="68" t="n">
@@ -8655,7 +8655,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="53"/>
       <c r="B81" s="53"/>
       <c r="C81" s="68" t="n">
@@ -8731,7 +8731,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="82" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="53"/>
       <c r="B82" s="53"/>
       <c r="C82" s="68" t="n">
@@ -8806,7 +8806,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="53"/>
       <c r="B83" s="53"/>
       <c r="C83" s="68" t="n">
@@ -8881,7 +8881,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="53"/>
       <c r="B84" s="53"/>
       <c r="C84" s="68" t="n">
@@ -8957,7 +8957,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="53"/>
       <c r="B85" s="53"/>
       <c r="C85" s="68" t="n">
@@ -9032,7 +9032,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="53"/>
       <c r="B86" s="53"/>
       <c r="C86" s="68" t="n">
@@ -9107,7 +9107,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="87" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="53"/>
       <c r="B87" s="53"/>
       <c r="C87" s="68" t="n">
@@ -9183,7 +9183,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="53"/>
       <c r="B88" s="53"/>
       <c r="C88" s="68" t="n">
@@ -9258,7 +9258,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="53"/>
       <c r="B89" s="53"/>
       <c r="C89" s="68" t="n">
@@ -9333,7 +9333,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="90" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="53"/>
       <c r="B90" s="53"/>
       <c r="C90" s="68" t="n">
@@ -9409,7 +9409,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="91" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="53"/>
       <c r="B91" s="53"/>
       <c r="C91" s="68" t="n">
@@ -9484,7 +9484,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="92" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="53"/>
       <c r="B92" s="53"/>
       <c r="C92" s="68" t="n">
@@ -9559,7 +9559,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="93" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="53"/>
       <c r="B93" s="53"/>
       <c r="C93" s="68" t="n">
@@ -9635,7 +9635,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="94" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="53"/>
       <c r="B94" s="53"/>
       <c r="C94" s="68" t="n">
@@ -9710,7 +9710,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="95" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="95" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="53"/>
       <c r="B95" s="53"/>
       <c r="C95" s="68" t="n">
@@ -9785,7 +9785,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="96" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="53"/>
       <c r="B96" s="53"/>
       <c r="C96" s="73" t="n">
@@ -9861,7 +9861,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="97" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="97" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="53"/>
       <c r="B97" s="53"/>
       <c r="C97" s="73" t="n">
@@ -9937,7 +9937,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="98" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="98" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="53"/>
       <c r="B98" s="53"/>
       <c r="C98" s="73" t="n">
@@ -10013,7 +10013,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="99" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="53"/>
       <c r="B99" s="53"/>
       <c r="C99" s="73" t="n">
@@ -10089,7 +10089,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="100" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="100" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="53"/>
       <c r="B100" s="53"/>
       <c r="C100" s="73" t="n">
@@ -10165,7 +10165,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="101" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="101" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="53"/>
       <c r="B101" s="53"/>
       <c r="C101" s="73" t="n">
@@ -10241,7 +10241,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="102" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="102" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="53"/>
       <c r="B102" s="53"/>
       <c r="C102" s="73" t="n">
@@ -10317,7 +10317,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="103" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="103" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="53"/>
       <c r="B103" s="53"/>
       <c r="C103" s="73" t="n">
@@ -10393,7 +10393,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="104" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="104" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="53"/>
       <c r="B104" s="53"/>
       <c r="C104" s="73" t="n">
@@ -10469,7 +10469,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="105" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="105" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="53"/>
       <c r="B105" s="53"/>
       <c r="C105" s="73" t="n">
@@ -10545,7 +10545,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="106" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="106" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="53"/>
       <c r="B106" s="53"/>
       <c r="C106" s="73" t="n">
@@ -10621,7 +10621,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="107" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="107" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="53"/>
       <c r="B107" s="53"/>
       <c r="C107" s="73" t="n">
@@ -10697,7 +10697,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="108" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="108" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="53"/>
       <c r="B108" s="53"/>
       <c r="C108" s="73" t="n">
@@ -10773,7 +10773,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="109" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="109" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="53"/>
       <c r="B109" s="53"/>
       <c r="C109" s="73" t="n">
@@ -10849,7 +10849,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="110" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="110" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="53"/>
       <c r="B110" s="53"/>
       <c r="C110" s="73" t="n">
@@ -10925,7 +10925,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="111" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="111" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="53"/>
       <c r="B111" s="53"/>
       <c r="C111" s="73" t="n">
@@ -11001,7 +11001,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="112" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="112" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="53"/>
       <c r="B112" s="53"/>
       <c r="C112" s="73" t="n">
@@ -11077,7 +11077,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="113" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="113" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="53"/>
       <c r="B113" s="53"/>
       <c r="C113" s="73" t="n">
@@ -11153,7 +11153,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="114" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="114" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="53"/>
       <c r="B114" s="53"/>
       <c r="C114" s="73" t="n">
@@ -11229,7 +11229,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="115" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="115" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="53"/>
       <c r="B115" s="53"/>
       <c r="C115" s="73" t="n">
@@ -11305,7 +11305,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="116" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="116" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="53"/>
       <c r="B116" s="53"/>
       <c r="C116" s="73" t="n">
@@ -11381,7 +11381,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="117" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="117" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="53"/>
       <c r="B117" s="53"/>
       <c r="C117" s="73" t="n">
@@ -11457,7 +11457,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="118" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="118" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="53"/>
       <c r="B118" s="53"/>
       <c r="C118" s="73" t="n">
@@ -11533,7 +11533,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="119" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="119" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="53"/>
       <c r="B119" s="53"/>
       <c r="C119" s="73" t="n">
@@ -11609,7 +11609,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="120" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="120" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="53"/>
       <c r="B120" s="53"/>
       <c r="C120" s="73" t="n">
@@ -11685,7 +11685,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="121" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="121" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="53"/>
       <c r="B121" s="53"/>
       <c r="C121" s="73" t="n">
@@ -11761,7 +11761,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="122" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="122" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="53"/>
       <c r="B122" s="53"/>
       <c r="C122" s="73" t="n">
@@ -11835,7 +11835,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="123" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="123" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="53"/>
       <c r="B123" s="53"/>
       <c r="C123" s="73" t="n">
@@ -11911,7 +11911,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="124" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="124" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="53"/>
       <c r="B124" s="53"/>
       <c r="C124" s="73" t="n">
@@ -11987,7 +11987,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="125" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="125" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="53"/>
       <c r="B125" s="53"/>
       <c r="C125" s="73" t="n">
@@ -12061,7 +12061,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="126" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="126" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="53"/>
       <c r="B126" s="53"/>
       <c r="C126" s="73" t="n">
@@ -12137,7 +12137,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="127" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="127" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="53"/>
       <c r="B127" s="53"/>
       <c r="C127" s="73" t="n">
@@ -12213,7 +12213,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="128" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="128" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A128" s="53"/>
       <c r="B128" s="53"/>
       <c r="C128" s="73" t="n">
@@ -12287,7 +12287,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="129" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="129" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A129" s="53"/>
       <c r="B129" s="53"/>
       <c r="C129" s="73" t="n">
@@ -12363,7 +12363,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="130" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="130" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A130" s="53"/>
       <c r="B130" s="53"/>
       <c r="C130" s="73" t="n">
@@ -12439,7 +12439,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="131" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="131" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A131" s="53"/>
       <c r="B131" s="53"/>
       <c r="C131" s="73" t="n">
@@ -12513,7 +12513,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="132" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="132" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="53"/>
       <c r="B132" s="53"/>
       <c r="C132" s="73" t="n">
@@ -12589,7 +12589,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="133" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="133" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A133" s="53"/>
       <c r="B133" s="53"/>
       <c r="C133" s="73" t="n">
@@ -12665,7 +12665,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="134" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="134" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A134" s="53"/>
       <c r="B134" s="53"/>
       <c r="C134" s="73" t="n">
@@ -12739,7 +12739,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="135" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="135" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A135" s="53"/>
       <c r="B135" s="53"/>
       <c r="C135" s="73" t="n">
@@ -12815,7 +12815,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="136" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="136" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A136" s="53"/>
       <c r="B136" s="53"/>
       <c r="C136" s="73" t="n">
@@ -12891,7 +12891,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="137" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="137" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A137" s="53"/>
       <c r="B137" s="53"/>
       <c r="C137" s="73" t="n">
@@ -12965,7 +12965,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="138" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="138" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A138" s="53"/>
       <c r="B138" s="53"/>
       <c r="C138" s="73" t="n">
@@ -13041,7 +13041,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="139" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="139" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A139" s="53"/>
       <c r="B139" s="53"/>
       <c r="C139" s="73" t="n">
@@ -13116,7 +13116,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="140" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="140" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A140" s="53"/>
       <c r="B140" s="53"/>
       <c r="C140" s="73" t="n">
@@ -13192,7 +13192,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="141" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="141" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A141" s="53"/>
       <c r="B141" s="53"/>
       <c r="C141" s="73" t="n">
@@ -13268,7 +13268,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="142" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="142" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A142" s="53"/>
       <c r="B142" s="53"/>
       <c r="C142" s="73" t="n">
@@ -13343,7 +13343,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="143" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="143" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A143" s="53"/>
       <c r="B143" s="53"/>
       <c r="C143" s="73" t="n">
@@ -13419,7 +13419,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="144" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="144" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A144" s="53"/>
       <c r="B144" s="53"/>
       <c r="C144" s="73" t="n">
@@ -13495,7 +13495,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="145" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="145" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A145" s="53"/>
       <c r="B145" s="53"/>
       <c r="C145" s="73" t="n">
@@ -13570,7 +13570,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="146" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="146" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A146" s="53"/>
       <c r="B146" s="53"/>
       <c r="C146" s="73" t="n">
@@ -13646,7 +13646,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="147" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="147" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A147" s="53"/>
       <c r="B147" s="53"/>
       <c r="C147" s="73" t="n">
@@ -13722,7 +13722,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="148" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="148" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A148" s="53"/>
       <c r="B148" s="53"/>
       <c r="C148" s="73" t="n">
@@ -13797,7 +13797,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="149" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="149" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A149" s="53"/>
       <c r="B149" s="53"/>
       <c r="C149" s="73" t="n">
@@ -13873,7 +13873,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="150" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="150" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A150" s="53"/>
       <c r="B150" s="53"/>
       <c r="C150" s="73" t="n">
@@ -13949,7 +13949,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="151" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="151" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A151" s="53"/>
       <c r="B151" s="53"/>
       <c r="C151" s="73" t="n">
@@ -14024,7 +14024,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="152" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="152" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A152" s="53"/>
       <c r="B152" s="53"/>
       <c r="C152" s="73" t="n">
@@ -14100,7 +14100,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="153" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="153" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A153" s="53"/>
       <c r="B153" s="53"/>
       <c r="C153" s="73" t="n">
@@ -14176,7 +14176,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="154" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="154" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A154" s="53"/>
       <c r="B154" s="53"/>
       <c r="C154" s="73" t="n">
@@ -14251,7 +14251,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="155" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="155" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A155" s="53"/>
       <c r="B155" s="53"/>
       <c r="C155" s="73" t="n">
@@ -14327,7 +14327,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="156" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="156" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A156" s="53"/>
       <c r="B156" s="53"/>
       <c r="C156" s="73" t="n">
@@ -14403,7 +14403,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="157" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="157" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A157" s="53"/>
       <c r="B157" s="53"/>
       <c r="C157" s="73" t="n">
@@ -14479,7 +14479,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="158" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="158" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A158" s="53"/>
       <c r="B158" s="53"/>
       <c r="C158" s="73" t="n">
@@ -14555,7 +14555,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="159" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="159" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A159" s="53"/>
       <c r="B159" s="53"/>
       <c r="C159" s="73" t="n">
@@ -14631,7 +14631,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="160" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="160" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A160" s="53"/>
       <c r="B160" s="53"/>
       <c r="C160" s="73" t="n">
@@ -14707,7 +14707,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="161" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="161" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A161" s="53"/>
       <c r="B161" s="53"/>
       <c r="C161" s="73" t="n">
@@ -14783,7 +14783,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="162" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="162" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A162" s="53"/>
       <c r="B162" s="53"/>
       <c r="C162" s="81" t="n">
@@ -14859,7 +14859,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="163" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="163" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A163" s="53"/>
       <c r="B163" s="53"/>
       <c r="C163" s="81" t="n">
@@ -14934,7 +14934,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="164" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="164" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A164" s="53"/>
       <c r="B164" s="53"/>
       <c r="C164" s="81" t="n">
@@ -15009,7 +15009,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="165" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="165" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A165" s="53"/>
       <c r="B165" s="53"/>
       <c r="C165" s="81" t="n">
@@ -15085,7 +15085,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="166" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="166" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A166" s="53"/>
       <c r="B166" s="53"/>
       <c r="C166" s="81" t="n">
@@ -15160,7 +15160,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="167" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="167" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A167" s="53"/>
       <c r="B167" s="53"/>
       <c r="C167" s="81" t="n">
@@ -15235,7 +15235,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="168" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="168" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A168" s="53"/>
       <c r="B168" s="53"/>
       <c r="C168" s="81" t="n">
@@ -15311,7 +15311,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="169" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="169" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A169" s="53"/>
       <c r="B169" s="53"/>
       <c r="C169" s="81" t="n">
@@ -15386,7 +15386,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="170" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="170" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A170" s="53"/>
       <c r="B170" s="53"/>
       <c r="C170" s="81" t="n">
@@ -15461,7 +15461,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="171" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="171" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A171" s="53"/>
       <c r="B171" s="53"/>
       <c r="C171" s="81" t="n">
@@ -15537,7 +15537,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="172" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="172" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="53"/>
       <c r="B172" s="53"/>
       <c r="C172" s="81" t="n">
@@ -15612,7 +15612,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="173" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="173" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A173" s="53"/>
       <c r="B173" s="53"/>
       <c r="C173" s="81" t="n">
@@ -15687,7 +15687,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="174" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="174" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A174" s="53"/>
       <c r="B174" s="53"/>
       <c r="C174" s="81" t="n">
@@ -15763,7 +15763,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="175" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="175" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A175" s="53"/>
       <c r="B175" s="53"/>
       <c r="C175" s="81" t="n">
@@ -15838,7 +15838,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="176" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="176" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A176" s="53"/>
       <c r="B176" s="53"/>
       <c r="C176" s="81" t="n">
@@ -15913,7 +15913,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="177" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="177" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A177" s="53"/>
       <c r="B177" s="53"/>
       <c r="C177" s="81" t="n">
@@ -15989,7 +15989,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="178" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="178" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A178" s="53"/>
       <c r="B178" s="53"/>
       <c r="C178" s="81" t="n">
@@ -16064,7 +16064,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="179" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="179" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A179" s="53"/>
       <c r="B179" s="53"/>
       <c r="C179" s="81" t="n">
@@ -16138,7 +16138,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="180" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="180" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A180" s="53"/>
       <c r="B180" s="53"/>
       <c r="C180" s="81" t="n">
@@ -16214,7 +16214,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="181" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="181" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="53"/>
       <c r="B181" s="53"/>
       <c r="C181" s="81" t="n">
@@ -16289,7 +16289,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="182" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="182" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A182" s="53"/>
       <c r="B182" s="53"/>
       <c r="C182" s="81" t="n">
@@ -16363,7 +16363,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="183" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="183" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A183" s="53"/>
       <c r="B183" s="53"/>
       <c r="C183" s="81" t="n">
@@ -16439,7 +16439,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="184" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="184" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A184" s="53"/>
       <c r="B184" s="53"/>
       <c r="C184" s="81" t="n">
@@ -16514,7 +16514,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="185" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="185" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A185" s="53"/>
       <c r="B185" s="53"/>
       <c r="C185" s="81" t="n">
@@ -16588,7 +16588,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="186" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="186" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A186" s="53"/>
       <c r="B186" s="53"/>
       <c r="C186" s="81" t="n">
@@ -16664,7 +16664,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="187" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="187" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A187" s="53"/>
       <c r="B187" s="53"/>
       <c r="C187" s="81" t="n">
@@ -16739,7 +16739,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="188" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="188" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A188" s="53"/>
       <c r="B188" s="53"/>
       <c r="C188" s="81" t="n">
@@ -16813,7 +16813,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="189" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="189" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A189" s="53"/>
       <c r="B189" s="53"/>
       <c r="C189" s="93" t="n">
@@ -16886,7 +16886,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="190" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="190" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A190" s="53"/>
       <c r="B190" s="53"/>
       <c r="C190" s="93" t="n">
@@ -16960,7 +16960,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="191" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="191" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A191" s="53"/>
       <c r="B191" s="53"/>
       <c r="C191" s="93" t="n">
@@ -17034,7 +17034,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="192" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="192" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A192" s="53"/>
       <c r="B192" s="53"/>
       <c r="C192" s="93" t="n">
@@ -17108,7 +17108,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="193" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="193" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A193" s="53"/>
       <c r="B193" s="53"/>
       <c r="C193" s="93" t="n">
@@ -17182,7 +17182,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="194" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="194" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A194" s="53"/>
       <c r="B194" s="53"/>
       <c r="C194" s="93" t="n">
@@ -17256,7 +17256,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="195" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="195" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A195" s="53"/>
       <c r="B195" s="53"/>
       <c r="C195" s="93" t="n">
@@ -17330,7 +17330,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="196" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="196" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A196" s="53"/>
       <c r="B196" s="53"/>
       <c r="C196" s="93" t="n">
@@ -17404,7 +17404,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="197" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="197" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A197" s="53"/>
       <c r="B197" s="53"/>
       <c r="C197" s="93" t="n">
@@ -17478,7 +17478,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="198" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="198" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A198" s="53"/>
       <c r="B198" s="53"/>
       <c r="C198" s="93" t="n">
@@ -17552,7 +17552,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="199" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="199" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A199" s="53"/>
       <c r="B199" s="53"/>
       <c r="C199" s="93" t="n">
@@ -17626,7 +17626,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="200" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="200" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A200" s="53"/>
       <c r="B200" s="53"/>
       <c r="C200" s="93" t="n">
@@ -17700,7 +17700,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="201" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="201" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A201" s="53"/>
       <c r="B201" s="53"/>
       <c r="C201" s="93" t="n">
@@ -17774,7 +17774,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="202" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="202" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A202" s="53"/>
       <c r="B202" s="53"/>
       <c r="C202" s="93" t="n">
@@ -17848,7 +17848,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="203" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="203" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A203" s="53"/>
       <c r="B203" s="53"/>
       <c r="C203" s="93" t="n">
@@ -17922,7 +17922,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="204" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="204" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A204" s="53"/>
       <c r="B204" s="53"/>
       <c r="C204" s="93" t="n">
@@ -17996,7 +17996,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="205" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="205" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A205" s="53"/>
       <c r="B205" s="53"/>
       <c r="C205" s="93" t="n">
@@ -18070,7 +18070,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="206" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="206" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A206" s="53"/>
       <c r="B206" s="53"/>
       <c r="C206" s="93" t="n">
@@ -18144,7 +18144,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="207" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="207" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A207" s="53"/>
       <c r="B207" s="53"/>
       <c r="C207" s="93" t="n">
@@ -18218,7 +18218,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="208" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="208" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A208" s="53"/>
       <c r="B208" s="53"/>
       <c r="C208" s="93" t="n">
@@ -18292,7 +18292,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="209" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="209" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A209" s="53"/>
       <c r="B209" s="53"/>
       <c r="C209" s="93" t="n">
@@ -18366,7 +18366,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="210" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="210" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A210" s="53"/>
       <c r="B210" s="53"/>
       <c r="C210" s="93" t="n">
@@ -18440,7 +18440,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="211" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="211" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A211" s="53"/>
       <c r="B211" s="53"/>
       <c r="C211" s="93" t="n">
@@ -18514,7 +18514,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="212" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="212" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A212" s="53"/>
       <c r="B212" s="53"/>
       <c r="C212" s="93" t="n">
@@ -18588,7 +18588,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="213" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="213" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A213" s="53"/>
       <c r="B213" s="53"/>
       <c r="C213" s="93" t="n">
@@ -18662,7 +18662,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="214" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="214" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A214" s="53"/>
       <c r="B214" s="53"/>
       <c r="C214" s="93" t="n">
@@ -18736,7 +18736,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="215" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="215" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A215" s="53"/>
       <c r="B215" s="53"/>
       <c r="C215" s="93" t="n">
@@ -18810,7 +18810,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="216" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="216" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A216" s="53"/>
       <c r="B216" s="53"/>
       <c r="C216" s="93" t="n">
@@ -18884,7 +18884,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="217" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="217" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A217" s="53"/>
       <c r="B217" s="53"/>
       <c r="C217" s="93" t="n">
@@ -18958,7 +18958,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="218" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="218" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A218" s="53"/>
       <c r="B218" s="53"/>
       <c r="C218" s="93" t="n">
@@ -19032,7 +19032,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="219" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="219" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A219" s="53"/>
       <c r="B219" s="53"/>
       <c r="C219" s="98" t="n">
@@ -19108,7 +19108,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="220" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="220" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A220" s="53"/>
       <c r="B220" s="53"/>
       <c r="C220" s="98" t="n">
@@ -19183,7 +19183,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="221" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="221" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A221" s="53"/>
       <c r="B221" s="53"/>
       <c r="C221" s="98" t="n">
@@ -19258,7 +19258,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="222" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="222" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A222" s="53"/>
       <c r="B222" s="53"/>
       <c r="C222" s="98" t="n">
@@ -19334,7 +19334,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="223" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="223" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A223" s="53"/>
       <c r="B223" s="53"/>
       <c r="C223" s="98" t="n">
@@ -19409,7 +19409,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="224" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="224" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A224" s="53"/>
       <c r="B224" s="53"/>
       <c r="C224" s="98" t="n">
@@ -19484,7 +19484,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="225" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="225" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A225" s="53"/>
       <c r="B225" s="53"/>
       <c r="C225" s="98" t="n">
@@ -19560,7 +19560,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="226" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="226" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A226" s="53"/>
       <c r="B226" s="53"/>
       <c r="C226" s="98" t="n">
@@ -19635,7 +19635,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="227" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="227" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A227" s="53"/>
       <c r="B227" s="53"/>
       <c r="C227" s="98" t="n">
@@ -19710,7 +19710,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="228" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="228" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A228" s="53"/>
       <c r="B228" s="53"/>
       <c r="C228" s="98" t="n">
@@ -19786,7 +19786,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="229" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="229" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A229" s="53"/>
       <c r="B229" s="53"/>
       <c r="C229" s="98" t="n">
@@ -19861,7 +19861,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="230" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="230" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A230" s="53"/>
       <c r="B230" s="53"/>
       <c r="C230" s="98" t="n">
@@ -19936,7 +19936,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="231" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="231" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A231" s="53"/>
       <c r="B231" s="53"/>
       <c r="C231" s="98" t="n">
@@ -20012,7 +20012,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="232" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="232" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A232" s="53"/>
       <c r="B232" s="53"/>
       <c r="C232" s="98" t="n">
@@ -20087,7 +20087,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="233" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="233" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A233" s="53"/>
       <c r="B233" s="53"/>
       <c r="C233" s="98" t="n">
@@ -20162,7 +20162,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="234" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="234" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A234" s="53"/>
       <c r="B234" s="53"/>
       <c r="C234" s="98" t="n">
@@ -20238,7 +20238,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="235" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="235" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A235" s="53"/>
       <c r="B235" s="53"/>
       <c r="C235" s="98" t="n">
@@ -20313,7 +20313,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="236" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="236" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A236" s="53"/>
       <c r="B236" s="53"/>
       <c r="C236" s="98" t="n">
@@ -20388,7 +20388,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="237" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="237" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A237" s="53"/>
       <c r="B237" s="53"/>
       <c r="C237" s="98" t="n">
@@ -20464,7 +20464,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="238" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="238" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A238" s="53"/>
       <c r="B238" s="53"/>
       <c r="C238" s="98" t="n">
@@ -20539,7 +20539,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="239" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="239" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A239" s="53"/>
       <c r="B239" s="53"/>
       <c r="C239" s="98" t="n">
@@ -20614,7 +20614,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="240" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="240" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A240" s="53"/>
       <c r="B240" s="53"/>
       <c r="C240" s="98" t="n">
@@ -20690,7 +20690,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="241" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="241" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A241" s="53"/>
       <c r="B241" s="53"/>
       <c r="C241" s="98" t="n">
@@ -20765,7 +20765,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="242" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="242" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A242" s="53"/>
       <c r="B242" s="53"/>
       <c r="C242" s="98" t="n">
@@ -20840,7 +20840,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="243" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="243" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A243" s="53"/>
       <c r="B243" s="53"/>
       <c r="C243" s="98" t="n">
@@ -20916,7 +20916,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="244" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="244" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A244" s="53"/>
       <c r="B244" s="53"/>
       <c r="C244" s="98" t="n">
@@ -20991,7 +20991,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="245" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="245" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A245" s="53"/>
       <c r="B245" s="53"/>
       <c r="C245" s="98" t="n">
@@ -21066,7 +21066,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="246" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="246" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A246" s="53"/>
       <c r="B246" s="53"/>
       <c r="C246" s="103" t="n">
@@ -21140,7 +21140,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="247" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="247" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A247" s="53"/>
       <c r="B247" s="53"/>
       <c r="C247" s="103" t="n">
@@ -21214,7 +21214,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="248" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="248" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A248" s="53"/>
       <c r="B248" s="53"/>
       <c r="C248" s="103" t="n">
@@ -21288,7 +21288,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="249" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="249" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A249" s="53"/>
       <c r="B249" s="53"/>
       <c r="C249" s="103" t="n">
@@ -21362,7 +21362,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="250" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="250" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A250" s="53"/>
       <c r="B250" s="53"/>
       <c r="C250" s="103" t="n">
@@ -21436,7 +21436,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="251" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="251" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A251" s="53"/>
       <c r="B251" s="53"/>
       <c r="C251" s="103" t="n">
@@ -21510,7 +21510,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="252" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="252" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A252" s="53"/>
       <c r="B252" s="53"/>
       <c r="C252" s="103" t="n">
@@ -21584,7 +21584,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="253" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="253" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A253" s="53"/>
       <c r="B253" s="53"/>
       <c r="C253" s="103" t="n">
@@ -21658,7 +21658,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="254" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="254" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A254" s="53"/>
       <c r="B254" s="53"/>
       <c r="C254" s="103" t="n">
@@ -21732,7 +21732,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="255" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="255" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A255" s="53"/>
       <c r="B255" s="53"/>
       <c r="C255" s="103" t="n">
@@ -21806,7 +21806,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="256" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="256" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A256" s="53"/>
       <c r="B256" s="53"/>
       <c r="C256" s="103" t="n">
@@ -21880,7 +21880,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="257" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="257" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A257" s="53"/>
       <c r="B257" s="53"/>
       <c r="C257" s="103" t="n">
@@ -21954,7 +21954,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="258" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="258" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A258" s="53"/>
       <c r="B258" s="53"/>
       <c r="C258" s="103" t="n">
@@ -22028,7 +22028,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="259" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="259" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A259" s="53"/>
       <c r="B259" s="53"/>
       <c r="C259" s="103" t="n">
@@ -22102,7 +22102,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="260" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="260" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A260" s="53"/>
       <c r="B260" s="53"/>
       <c r="C260" s="103" t="n">
@@ -22176,7 +22176,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="261" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="261" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A261" s="53"/>
       <c r="B261" s="53"/>
       <c r="C261" s="103" t="n">
@@ -22250,7 +22250,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="262" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="262" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A262" s="53"/>
       <c r="B262" s="53"/>
       <c r="C262" s="103" t="n">
@@ -22324,7 +22324,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="263" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="263" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A263" s="53"/>
       <c r="B263" s="53"/>
       <c r="C263" s="103" t="n">
@@ -22398,7 +22398,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="264" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="264" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A264" s="53"/>
       <c r="B264" s="53"/>
       <c r="C264" s="103" t="n">
@@ -22472,7 +22472,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="265" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="265" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A265" s="53"/>
       <c r="B265" s="53"/>
       <c r="C265" s="103" t="n">
@@ -22546,7 +22546,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="266" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="266" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A266" s="53"/>
       <c r="B266" s="53"/>
       <c r="C266" s="103" t="n">
@@ -22620,7 +22620,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="267" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="267" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A267" s="53"/>
       <c r="B267" s="53"/>
       <c r="C267" s="103" t="n">
@@ -22694,7 +22694,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="268" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="268" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A268" s="53"/>
       <c r="B268" s="53"/>
       <c r="C268" s="103" t="n">
@@ -22768,7 +22768,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="269" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="269" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A269" s="53"/>
       <c r="B269" s="53"/>
       <c r="C269" s="103" t="n">
@@ -22842,7 +22842,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="270" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="270" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A270" s="53"/>
       <c r="B270" s="53"/>
       <c r="C270" s="108" t="n">
@@ -22916,7 +22916,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="271" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="271" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A271" s="53"/>
       <c r="B271" s="53"/>
       <c r="C271" s="108" t="n">
@@ -22989,7 +22989,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="272" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="272" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A272" s="53"/>
       <c r="B272" s="53"/>
       <c r="C272" s="108" t="n">
@@ -23062,7 +23062,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="273" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="273" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A273" s="53"/>
       <c r="B273" s="53"/>
       <c r="C273" s="108" t="n">
@@ -23136,7 +23136,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="274" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="274" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A274" s="53"/>
       <c r="B274" s="53"/>
       <c r="C274" s="108" t="n">
@@ -23209,7 +23209,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="275" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="275" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A275" s="53"/>
       <c r="B275" s="53"/>
       <c r="C275" s="108" t="n">
@@ -23282,7 +23282,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="276" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="276" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A276" s="53"/>
       <c r="B276" s="53"/>
       <c r="C276" s="108" t="n">
@@ -23356,7 +23356,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="277" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="277" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A277" s="53"/>
       <c r="B277" s="53"/>
       <c r="C277" s="108" t="n">
@@ -23429,7 +23429,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="278" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="278" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A278" s="53"/>
       <c r="B278" s="53"/>
       <c r="C278" s="108" t="n">
@@ -23502,7 +23502,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="279" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="279" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A279" s="53"/>
       <c r="B279" s="53"/>
       <c r="C279" s="108" t="n">
@@ -23576,7 +23576,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="280" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="280" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A280" s="53"/>
       <c r="B280" s="53"/>
       <c r="C280" s="108" t="n">
@@ -23649,7 +23649,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="281" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="281" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A281" s="53"/>
       <c r="B281" s="53"/>
       <c r="C281" s="108" t="n">
@@ -23722,7 +23722,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="282" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="282" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A282" s="53"/>
       <c r="B282" s="53"/>
       <c r="C282" s="108" t="n">
@@ -23796,7 +23796,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="283" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="283" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A283" s="53"/>
       <c r="B283" s="53"/>
       <c r="C283" s="108" t="n">
@@ -23869,7 +23869,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="284" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="284" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A284" s="53"/>
       <c r="B284" s="53"/>
       <c r="C284" s="108" t="n">
@@ -23942,7 +23942,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="285" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="285" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A285" s="53"/>
       <c r="B285" s="53"/>
       <c r="C285" s="108" t="n">
@@ -24016,7 +24016,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="286" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="286" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A286" s="53"/>
       <c r="B286" s="53"/>
       <c r="C286" s="108" t="n">
@@ -24089,7 +24089,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="287" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="287" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A287" s="53"/>
       <c r="B287" s="53"/>
       <c r="C287" s="108" t="n">
@@ -24162,7 +24162,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="288" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="288" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A288" s="53"/>
       <c r="B288" s="53"/>
       <c r="C288" s="108" t="n">
@@ -24236,7 +24236,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="289" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="289" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A289" s="53"/>
       <c r="B289" s="53"/>
       <c r="C289" s="108" t="n">
@@ -24309,7 +24309,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="290" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="290" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A290" s="53"/>
       <c r="B290" s="53"/>
       <c r="C290" s="113" t="n">
@@ -24385,7 +24385,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="291" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="291" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A291" s="53"/>
       <c r="B291" s="53"/>
       <c r="C291" s="113" t="n">
@@ -24460,7 +24460,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="292" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="292" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A292" s="53"/>
       <c r="B292" s="53"/>
       <c r="C292" s="113" t="n">
@@ -24535,7 +24535,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="293" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="293" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A293" s="53"/>
       <c r="B293" s="53"/>
       <c r="C293" s="113" t="n">
@@ -24610,7 +24610,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="294" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="294" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A294" s="53"/>
       <c r="B294" s="53"/>
       <c r="C294" s="113" t="n">
@@ -24686,7 +24686,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="295" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="295" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A295" s="53"/>
       <c r="B295" s="53"/>
       <c r="C295" s="113" t="n">
@@ -24761,7 +24761,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="296" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="296" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A296" s="53"/>
       <c r="B296" s="53"/>
       <c r="C296" s="113" t="n">
@@ -24836,7 +24836,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="297" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="297" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A297" s="53"/>
       <c r="B297" s="53"/>
       <c r="C297" s="113" t="n">
@@ -24911,7 +24911,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="298" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="298" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A298" s="53"/>
       <c r="B298" s="53"/>
       <c r="C298" s="113" t="n">
@@ -24987,7 +24987,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="299" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="299" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A299" s="53"/>
       <c r="B299" s="53"/>
       <c r="C299" s="113" t="n">
@@ -25062,7 +25062,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="300" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="300" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A300" s="53"/>
       <c r="B300" s="53"/>
       <c r="C300" s="113" t="n">
@@ -25137,7 +25137,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="301" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="301" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A301" s="53"/>
       <c r="B301" s="53"/>
       <c r="C301" s="113" t="n">
@@ -25213,7 +25213,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="302" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="302" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A302" s="53"/>
       <c r="B302" s="53"/>
       <c r="C302" s="113" t="n">
@@ -25288,7 +25288,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="303" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="303" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A303" s="53"/>
       <c r="B303" s="53"/>
       <c r="C303" s="113" t="n">
@@ -25363,7 +25363,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="304" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="304" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A304" s="53"/>
       <c r="B304" s="53"/>
       <c r="C304" s="113" t="n">
@@ -25438,7 +25438,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="305" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="305" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A305" s="53"/>
       <c r="B305" s="53"/>
       <c r="C305" s="113" t="n">
@@ -25514,7 +25514,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="306" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="306" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A306" s="53"/>
       <c r="B306" s="53"/>
       <c r="C306" s="113" t="n">
@@ -25589,7 +25589,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="307" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="307" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A307" s="53"/>
       <c r="B307" s="53"/>
       <c r="C307" s="113" t="n">
@@ -25664,7 +25664,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="308" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="308" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A308" s="53"/>
       <c r="B308" s="53"/>
       <c r="C308" s="113" t="n">
@@ -25739,7 +25739,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="309" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="309" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A309" s="53"/>
       <c r="B309" s="53"/>
       <c r="C309" s="113" t="n">
@@ -25815,7 +25815,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="310" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="310" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A310" s="53"/>
       <c r="B310" s="53"/>
       <c r="C310" s="113" t="n">
@@ -25890,7 +25890,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="311" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="311" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A311" s="53"/>
       <c r="B311" s="53"/>
       <c r="C311" s="113" t="n">
@@ -25965,7 +25965,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="312" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="312" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A312" s="53"/>
       <c r="B312" s="53"/>
       <c r="C312" s="113" t="n">
@@ -26041,7 +26041,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="313" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="313" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A313" s="53"/>
       <c r="B313" s="53"/>
       <c r="C313" s="113" t="n">
@@ -26116,7 +26116,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="314" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="314" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A314" s="53"/>
       <c r="B314" s="53"/>
       <c r="C314" s="113" t="n">
@@ -26191,7 +26191,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="315" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="315" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A315" s="53"/>
       <c r="B315" s="53"/>
       <c r="C315" s="113" t="n">
@@ -26267,7 +26267,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="316" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="316" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A316" s="53"/>
       <c r="B316" s="53"/>
       <c r="C316" s="113" t="n">
@@ -26342,7 +26342,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="317" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="317" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A317" s="53"/>
       <c r="B317" s="53"/>
       <c r="C317" s="113" t="n">
@@ -26417,7 +26417,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="318" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="318" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A318" s="53"/>
       <c r="B318" s="53"/>
       <c r="C318" s="113" t="n">
@@ -26493,7 +26493,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="319" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="319" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A319" s="53"/>
       <c r="B319" s="53"/>
       <c r="C319" s="113" t="n">
@@ -26568,7 +26568,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="320" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="320" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A320" s="53"/>
       <c r="B320" s="53"/>
       <c r="C320" s="113" t="n">
@@ -26643,7 +26643,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="321" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="321" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A321" s="53"/>
       <c r="B321" s="53"/>
       <c r="C321" s="118" t="n">
@@ -26717,7 +26717,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="322" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="322" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A322" s="53"/>
       <c r="B322" s="53"/>
       <c r="C322" s="118" t="n">
@@ -26791,7 +26791,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="323" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="323" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A323" s="53"/>
       <c r="B323" s="53"/>
       <c r="C323" s="118" t="n">
@@ -26865,7 +26865,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="324" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="324" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A324" s="53"/>
       <c r="B324" s="53"/>
       <c r="C324" s="118" t="n">
@@ -26939,7 +26939,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="325" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="325" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A325" s="53"/>
       <c r="B325" s="53"/>
       <c r="C325" s="118" t="n">
@@ -27013,7 +27013,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="326" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="326" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A326" s="53"/>
       <c r="B326" s="53"/>
       <c r="C326" s="118" t="n">
@@ -27087,7 +27087,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="327" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="327" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A327" s="53"/>
       <c r="B327" s="53"/>
       <c r="C327" s="118" t="n">
@@ -27161,7 +27161,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="328" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="328" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A328" s="53"/>
       <c r="B328" s="53"/>
       <c r="C328" s="118" t="n">
@@ -27235,7 +27235,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="329" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="329" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A329" s="53"/>
       <c r="B329" s="53"/>
       <c r="C329" s="118" t="n">
@@ -27309,7 +27309,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="330" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="330" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A330" s="53"/>
       <c r="B330" s="53"/>
       <c r="C330" s="118" t="n">
@@ -27383,7 +27383,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="331" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="331" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A331" s="53"/>
       <c r="B331" s="53"/>
       <c r="C331" s="118" t="n">
@@ -27457,7 +27457,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="332" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="332" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A332" s="53"/>
       <c r="B332" s="53"/>
       <c r="C332" s="118" t="n">
@@ -27531,7 +27531,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="333" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="333" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A333" s="53"/>
       <c r="B333" s="53"/>
       <c r="C333" s="118" t="n">
@@ -27605,7 +27605,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="334" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="334" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A334" s="53"/>
       <c r="B334" s="53"/>
       <c r="C334" s="118" t="n">
@@ -27679,7 +27679,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="335" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="335" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A335" s="53"/>
       <c r="B335" s="53"/>
       <c r="C335" s="118" t="n">
@@ -27753,7 +27753,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="336" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="336" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A336" s="53"/>
       <c r="B336" s="53"/>
       <c r="C336" s="118" t="n">
@@ -27827,7 +27827,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="337" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="337" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A337" s="53"/>
       <c r="B337" s="53"/>
       <c r="C337" s="118" t="n">
@@ -27901,7 +27901,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="338" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="338" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A338" s="53"/>
       <c r="B338" s="53"/>
       <c r="C338" s="118" t="n">
@@ -27975,7 +27975,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="339" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="339" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A339" s="53"/>
       <c r="B339" s="53"/>
       <c r="C339" s="118" t="n">
@@ -28049,7 +28049,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="340" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="340" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A340" s="53"/>
       <c r="B340" s="53"/>
       <c r="C340" s="118" t="n">
@@ -28123,7 +28123,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="341" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="341" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A341" s="53"/>
       <c r="B341" s="53"/>
       <c r="C341" s="118" t="n">
@@ -28197,7 +28197,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="342" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="342" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A342" s="53"/>
       <c r="B342" s="53"/>
       <c r="C342" s="118" t="n">
@@ -28271,7 +28271,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="343" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="343" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A343" s="53"/>
       <c r="B343" s="53"/>
       <c r="C343" s="118" t="n">
@@ -28345,7 +28345,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="344" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="344" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A344" s="53"/>
       <c r="B344" s="53"/>
       <c r="C344" s="118" t="n">
@@ -28419,7 +28419,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="345" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="345" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A345" s="53"/>
       <c r="B345" s="53"/>
       <c r="C345" s="123" t="n">
@@ -28493,7 +28493,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="346" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="346" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A346" s="53"/>
       <c r="B346" s="53"/>
       <c r="C346" s="123" t="n">
@@ -28566,7 +28566,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="347" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="347" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A347" s="53"/>
       <c r="B347" s="53"/>
       <c r="C347" s="123" t="n">
@@ -28639,7 +28639,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="348" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="348" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A348" s="53"/>
       <c r="B348" s="53"/>
       <c r="C348" s="123" t="n">
@@ -28712,7 +28712,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="349" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="349" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A349" s="53"/>
       <c r="B349" s="53"/>
       <c r="C349" s="123" t="n">
@@ -28785,7 +28785,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="350" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="350" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A350" s="53"/>
       <c r="B350" s="53"/>
       <c r="C350" s="123" t="n">
@@ -28858,7 +28858,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="351" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="351" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A351" s="53"/>
       <c r="B351" s="53"/>
       <c r="C351" s="123" t="n">
@@ -28932,7 +28932,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="352" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="352" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A352" s="53"/>
       <c r="B352" s="53"/>
       <c r="C352" s="123" t="n">
@@ -29005,7 +29005,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="353" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="353" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A353" s="53"/>
       <c r="B353" s="53"/>
       <c r="C353" s="128" t="n">
@@ -29079,7 +29079,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="354" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="354" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A354" s="53"/>
       <c r="B354" s="53"/>
       <c r="C354" s="128" t="n">
@@ -29152,7 +29152,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="355" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="355" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A355" s="53"/>
       <c r="B355" s="53"/>
       <c r="C355" s="128" t="n">
@@ -29225,7 +29225,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="356" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="356" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A356" s="53"/>
       <c r="B356" s="53"/>
       <c r="C356" s="133" t="n">
@@ -29301,7 +29301,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="357" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="357" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A357" s="53"/>
       <c r="B357" s="53"/>
       <c r="C357" s="133" t="n">
@@ -29377,7 +29377,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="358" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="358" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A358" s="53"/>
       <c r="B358" s="53"/>
       <c r="C358" s="133" t="n">
@@ -29453,7 +29453,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="359" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="359" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A359" s="53"/>
       <c r="B359" s="53"/>
       <c r="C359" s="133" t="n">
@@ -29529,7 +29529,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="360" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="360" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A360" s="53"/>
       <c r="B360" s="53"/>
       <c r="C360" s="133" t="n">
@@ -29605,7 +29605,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="361" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="361" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A361" s="53"/>
       <c r="B361" s="53"/>
       <c r="C361" s="133" t="n">
@@ -29681,7 +29681,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="362" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="362" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A362" s="53"/>
       <c r="B362" s="53"/>
       <c r="C362" s="133" t="n">
@@ -29757,7 +29757,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="363" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="363" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A363" s="53"/>
       <c r="B363" s="53"/>
       <c r="C363" s="133" t="n">
@@ -29833,7 +29833,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="364" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="364" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A364" s="53"/>
       <c r="B364" s="53"/>
       <c r="C364" s="133" t="n">
@@ -29909,7 +29909,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="365" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="365" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A365" s="53"/>
       <c r="B365" s="53"/>
       <c r="C365" s="133" t="n">
@@ -29985,7 +29985,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="366" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="366" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A366" s="53"/>
       <c r="B366" s="53"/>
       <c r="C366" s="133" t="n">
@@ -30061,7 +30061,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="367" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="367" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A367" s="53"/>
       <c r="B367" s="53"/>
       <c r="C367" s="133" t="n">
@@ -30137,7 +30137,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="368" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="368" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A368" s="53"/>
       <c r="B368" s="53"/>
       <c r="C368" s="133" t="n">
@@ -30213,7 +30213,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="369" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="369" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A369" s="53"/>
       <c r="B369" s="53"/>
       <c r="C369" s="133" t="n">
@@ -30289,7 +30289,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="370" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="370" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A370" s="53"/>
       <c r="B370" s="53"/>
       <c r="C370" s="142" t="n">
@@ -30363,7 +30363,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="371" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="371" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A371" s="53"/>
       <c r="B371" s="53"/>
       <c r="C371" s="142" t="n">
@@ -30437,7 +30437,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="372" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="372" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A372" s="53"/>
       <c r="B372" s="53"/>
       <c r="C372" s="142" t="n">
@@ -30511,7 +30511,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="373" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="373" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A373" s="53"/>
       <c r="B373" s="53"/>
       <c r="C373" s="142" t="n">
@@ -30585,7 +30585,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="374" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="374" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A374" s="53"/>
       <c r="B374" s="53"/>
       <c r="C374" s="142" t="n">
@@ -30659,7 +30659,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="375" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="375" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A375" s="53"/>
       <c r="B375" s="53"/>
       <c r="C375" s="142" t="n">
@@ -30733,7 +30733,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="376" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="376" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A376" s="53"/>
       <c r="B376" s="53"/>
       <c r="C376" s="142" t="n">
@@ -30807,7 +30807,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="377" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="377" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A377" s="53"/>
       <c r="B377" s="53"/>
       <c r="C377" s="142" t="n">
@@ -30881,7 +30881,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="378" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="378" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A378" s="53"/>
       <c r="B378" s="53"/>
       <c r="C378" s="142" t="n">
@@ -30955,7 +30955,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="379" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="379" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A379" s="53"/>
       <c r="B379" s="53"/>
       <c r="C379" s="142" t="n">
@@ -31029,7 +31029,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="380" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="380" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A380" s="53"/>
       <c r="B380" s="53"/>
       <c r="C380" s="142" t="n">
@@ -31103,7 +31103,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="381" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="381" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A381" s="53"/>
       <c r="B381" s="53"/>
       <c r="C381" s="142" t="n">
@@ -31177,7 +31177,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="382" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="382" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A382" s="53"/>
       <c r="B382" s="53"/>
       <c r="C382" s="142" t="n">
@@ -31251,7 +31251,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="383" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="383" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A383" s="53"/>
       <c r="B383" s="53"/>
       <c r="C383" s="142" t="n">
@@ -31325,7 +31325,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="384" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="384" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A384" s="53"/>
       <c r="B384" s="53"/>
       <c r="C384" s="142" t="n">
@@ -31399,7 +31399,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="385" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="385" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A385" s="53"/>
       <c r="B385" s="53"/>
       <c r="C385" s="142" t="n">
@@ -31473,7 +31473,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="386" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="386" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A386" s="53"/>
       <c r="B386" s="53"/>
       <c r="C386" s="142" t="n">
@@ -31547,7 +31547,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="387" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="387" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A387" s="53"/>
       <c r="B387" s="53"/>
       <c r="C387" s="142" t="n">
@@ -31621,7 +31621,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="388" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="388" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A388" s="53"/>
       <c r="B388" s="53"/>
       <c r="C388" s="148" t="n">
@@ -31695,7 +31695,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="389" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="389" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A389" s="53"/>
       <c r="B389" s="53"/>
       <c r="C389" s="148" t="n">
@@ -31769,7 +31769,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="390" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="390" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A390" s="53"/>
       <c r="B390" s="53"/>
       <c r="C390" s="148" t="n">
@@ -31843,7 +31843,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="391" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="391" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A391" s="53"/>
       <c r="B391" s="53"/>
       <c r="C391" s="148" t="n">
@@ -31917,7 +31917,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="392" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="392" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A392" s="53"/>
       <c r="B392" s="53"/>
       <c r="C392" s="148" t="n">
@@ -31991,7 +31991,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="393" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="393" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A393" s="53"/>
       <c r="B393" s="53"/>
       <c r="C393" s="148" t="n">
@@ -32065,7 +32065,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="394" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="394" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A394" s="53"/>
       <c r="B394" s="53"/>
       <c r="C394" s="148" t="n">
@@ -32139,7 +32139,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="395" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="395" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A395" s="53"/>
       <c r="B395" s="53"/>
       <c r="C395" s="148" t="n">
@@ -32213,7 +32213,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="396" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="396" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A396" s="53"/>
       <c r="B396" s="53"/>
       <c r="C396" s="148" t="n">
@@ -32287,7 +32287,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="397" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="397" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A397" s="53"/>
       <c r="B397" s="53"/>
       <c r="C397" s="148" t="n">
@@ -32361,7 +32361,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="398" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="398" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A398" s="53"/>
       <c r="B398" s="53"/>
       <c r="C398" s="148" t="n">
@@ -32435,7 +32435,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="399" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="399" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A399" s="53"/>
       <c r="B399" s="53"/>
       <c r="C399" s="148" t="n">
@@ -32509,7 +32509,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="400" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="400" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A400" s="53"/>
       <c r="B400" s="53"/>
       <c r="C400" s="148" t="n">
@@ -32583,7 +32583,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="401" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="401" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A401" s="53"/>
       <c r="B401" s="53"/>
       <c r="C401" s="148" t="n">
@@ -32657,7 +32657,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="402" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="402" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A402" s="53"/>
       <c r="B402" s="53"/>
       <c r="C402" s="148" t="n">
@@ -32731,7 +32731,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="403" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="403" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A403" s="53"/>
       <c r="B403" s="53"/>
       <c r="C403" s="148" t="n">
@@ -32805,7 +32805,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="404" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="404" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A404" s="53"/>
       <c r="B404" s="53"/>
       <c r="C404" s="148" t="n">
@@ -32879,7 +32879,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="405" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="405" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A405" s="53"/>
       <c r="B405" s="53"/>
       <c r="C405" s="148" t="n">
@@ -32953,7 +32953,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="406" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="406" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A406" s="53"/>
       <c r="B406" s="53"/>
       <c r="C406" s="154" t="n">
@@ -33027,7 +33027,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="407" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="407" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A407" s="53"/>
       <c r="B407" s="53"/>
       <c r="C407" s="154" t="n">
@@ -33101,7 +33101,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="408" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="408" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A408" s="53"/>
       <c r="B408" s="53"/>
       <c r="C408" s="154" t="n">
@@ -33175,7 +33175,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="409" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="409" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A409" s="53"/>
       <c r="B409" s="53"/>
       <c r="C409" s="154" t="n">
@@ -33249,7 +33249,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="410" s="167" customFormat="true" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="410" s="167" customFormat="true" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A410" s="160"/>
       <c r="B410" s="160"/>
       <c r="C410" s="161" t="n">
@@ -33323,7 +33323,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="411" s="167" customFormat="true" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="411" s="167" customFormat="true" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A411" s="160"/>
       <c r="B411" s="160"/>
       <c r="C411" s="161" t="n">
@@ -33397,7 +33397,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="412" s="167" customFormat="true" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="412" s="167" customFormat="true" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A412" s="160"/>
       <c r="B412" s="160"/>
       <c r="C412" s="161" t="n">
@@ -33471,7 +33471,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="413" s="167" customFormat="true" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="413" s="167" customFormat="true" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A413" s="160"/>
       <c r="B413" s="160"/>
       <c r="C413" s="161" t="n">
@@ -33545,7 +33545,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="414" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="414" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A414" s="53"/>
       <c r="B414" s="53"/>
       <c r="C414" s="154" t="n">
@@ -33619,7 +33619,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="415" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="415" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A415" s="53"/>
       <c r="B415" s="53"/>
       <c r="C415" s="154" t="n">
@@ -33693,7 +33693,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="416" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="416" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A416" s="53"/>
       <c r="B416" s="53"/>
       <c r="C416" s="154" t="n">
@@ -33767,7 +33767,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="417" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="417" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A417" s="53"/>
       <c r="B417" s="53"/>
       <c r="C417" s="154" t="n">
@@ -33841,7 +33841,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="418" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="418" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A418" s="53"/>
       <c r="B418" s="53"/>
       <c r="C418" s="154" t="n">
@@ -33915,7 +33915,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="419" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="419" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A419" s="53"/>
       <c r="B419" s="53"/>
       <c r="C419" s="154" t="n">
@@ -33989,7 +33989,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="420" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="420" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A420" s="53"/>
       <c r="B420" s="53"/>
       <c r="C420" s="154" t="n">
@@ -34063,7 +34063,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="421" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="421" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A421" s="53"/>
       <c r="B421" s="53"/>
       <c r="C421" s="154" t="n">
@@ -34137,7 +34137,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="422" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="422" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A422" s="53"/>
       <c r="B422" s="53"/>
       <c r="C422" s="154" t="n">
@@ -34211,7 +34211,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="423" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="423" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A423" s="53"/>
       <c r="B423" s="53"/>
       <c r="C423" s="154" t="n">
@@ -34285,7 +34285,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="424" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="424" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A424" s="53"/>
       <c r="B424" s="53"/>
       <c r="C424" s="154" t="n">
@@ -34359,7 +34359,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="425" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="425" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A425" s="53"/>
       <c r="B425" s="53"/>
       <c r="C425" s="154" t="n">
@@ -34433,7 +34433,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="426" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="426" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A426" s="53"/>
       <c r="B426" s="53"/>
       <c r="C426" s="154" t="n">
@@ -34507,7 +34507,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="427" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="427" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A427" s="53"/>
       <c r="B427" s="53"/>
       <c r="C427" s="154" t="n">
@@ -34581,7 +34581,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="428" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="428" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A428" s="53"/>
       <c r="B428" s="53"/>
       <c r="C428" s="154" t="n">
@@ -34655,7 +34655,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="429" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="429" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A429" s="53"/>
       <c r="B429" s="53"/>
       <c r="C429" s="154" t="n">
@@ -34729,7 +34729,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="430" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="430" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A430" s="53"/>
       <c r="B430" s="53"/>
       <c r="C430" s="154" t="n">
@@ -34803,7 +34803,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="431" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="431" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A431" s="53"/>
       <c r="B431" s="53"/>
       <c r="C431" s="154" t="n">
@@ -34877,7 +34877,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="432" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="432" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A432" s="53"/>
       <c r="B432" s="53"/>
       <c r="C432" s="154" t="n">
@@ -34951,7 +34951,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="433" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="433" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A433" s="53"/>
       <c r="B433" s="53"/>
       <c r="C433" s="154" t="n">
@@ -35025,7 +35025,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="434" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="434" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A434" s="53"/>
       <c r="B434" s="53"/>
       <c r="C434" s="154" t="n">
@@ -35099,7 +35099,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="435" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="435" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A435" s="53"/>
       <c r="B435" s="53"/>
       <c r="C435" s="154" t="n">
@@ -35173,7 +35173,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="436" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="436" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A436" s="53"/>
       <c r="B436" s="53"/>
       <c r="C436" s="154" t="n">
@@ -35247,7 +35247,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="437" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="437" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A437" s="53"/>
       <c r="B437" s="53"/>
       <c r="C437" s="154" t="n">
@@ -35321,7 +35321,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="438" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="438" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A438" s="53"/>
       <c r="B438" s="53"/>
       <c r="C438" s="154" t="n">
@@ -35394,7 +35394,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="439" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="439" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A439" s="53"/>
       <c r="B439" s="53"/>
       <c r="C439" s="154" t="n">
@@ -35467,7 +35467,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="440" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="440" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A440" s="53"/>
       <c r="B440" s="53"/>
       <c r="C440" s="154" t="n">
@@ -35540,7 +35540,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="441" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="441" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A441" s="53"/>
       <c r="B441" s="53"/>
       <c r="C441" s="154" t="n">
@@ -35613,7 +35613,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="442" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="442" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A442" s="53"/>
       <c r="B442" s="53"/>
       <c r="C442" s="154" t="n">
@@ -35687,7 +35687,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="443" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="443" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A443" s="53"/>
       <c r="B443" s="53"/>
       <c r="C443" s="154" t="n">
@@ -35761,7 +35761,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="444" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="444" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A444" s="53"/>
       <c r="B444" s="53"/>
       <c r="C444" s="154" t="n">
@@ -35835,7 +35835,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="445" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="445" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A445" s="53"/>
       <c r="B445" s="53"/>
       <c r="C445" s="154" t="n">
@@ -35909,7 +35909,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="446" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="446" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A446" s="53"/>
       <c r="B446" s="53"/>
       <c r="C446" s="154" t="n">
@@ -35983,7 +35983,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="447" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="447" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A447" s="53"/>
       <c r="B447" s="53"/>
       <c r="C447" s="154" t="n">
@@ -36057,7 +36057,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="448" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="448" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A448" s="53"/>
       <c r="B448" s="53"/>
       <c r="C448" s="154" t="n">
@@ -36131,7 +36131,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="449" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="449" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A449" s="53"/>
       <c r="B449" s="53"/>
       <c r="C449" s="154" t="n">
@@ -36205,7 +36205,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="450" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="450" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A450" s="53"/>
       <c r="B450" s="53"/>
       <c r="C450" s="154" t="n">
@@ -36279,7 +36279,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="451" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="451" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A451" s="53"/>
       <c r="B451" s="53"/>
       <c r="C451" s="154" t="n">
@@ -36353,7 +36353,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="452" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="452" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A452" s="53"/>
       <c r="B452" s="53"/>
       <c r="C452" s="154" t="n">
@@ -36427,7 +36427,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="453" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="453" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A453" s="53"/>
       <c r="B453" s="53"/>
       <c r="C453" s="154" t="n">
@@ -36500,7 +36500,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="454" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="454" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A454" s="53"/>
       <c r="B454" s="53"/>
       <c r="C454" s="154" t="n">
@@ -36574,7 +36574,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="455" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="455" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A455" s="53"/>
       <c r="B455" s="53"/>
       <c r="C455" s="154" t="n">
@@ -36648,7 +36648,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="456" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="456" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A456" s="53"/>
       <c r="B456" s="53"/>
       <c r="C456" s="168" t="n">
@@ -36722,7 +36722,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="457" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="457" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A457" s="53"/>
       <c r="B457" s="53"/>
       <c r="C457" s="168" t="n">
@@ -36796,7 +36796,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="458" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="458" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A458" s="53"/>
       <c r="B458" s="53"/>
       <c r="C458" s="168" t="n">
@@ -36870,7 +36870,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="459" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="459" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A459" s="53"/>
       <c r="B459" s="53"/>
       <c r="C459" s="168" t="n">
@@ -36944,7 +36944,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="460" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="460" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A460" s="53"/>
       <c r="B460" s="53"/>
       <c r="C460" s="168" t="n">
@@ -37018,7 +37018,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="461" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="461" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A461" s="53"/>
       <c r="B461" s="53"/>
       <c r="C461" s="168" t="n">
@@ -37092,7 +37092,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="462" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="462" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A462" s="53"/>
       <c r="B462" s="53"/>
       <c r="C462" s="168" t="n">
@@ -37166,7 +37166,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="463" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="463" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A463" s="53"/>
       <c r="B463" s="53"/>
       <c r="C463" s="168" t="n">
@@ -37240,7 +37240,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="464" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="464" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A464" s="53"/>
       <c r="B464" s="53"/>
       <c r="C464" s="168" t="n">
@@ -37314,7 +37314,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="465" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="465" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A465" s="53"/>
       <c r="B465" s="53"/>
       <c r="C465" s="168" t="n">
@@ -37388,7 +37388,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="466" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="466" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A466" s="53"/>
       <c r="B466" s="53"/>
       <c r="C466" s="168" t="n">
@@ -37462,7 +37462,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="467" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="467" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A467" s="53"/>
       <c r="B467" s="53"/>
       <c r="C467" s="168" t="n">
@@ -37536,7 +37536,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="468" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="468" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A468" s="53"/>
       <c r="B468" s="53"/>
       <c r="C468" s="168" t="n">
@@ -37610,7 +37610,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="469" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="469" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A469" s="53"/>
       <c r="B469" s="53"/>
       <c r="C469" s="168" t="n">
@@ -37684,7 +37684,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="470" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="470" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A470" s="53"/>
       <c r="B470" s="53"/>
       <c r="C470" s="168" t="n">
@@ -37758,7 +37758,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="471" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="471" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A471" s="53"/>
       <c r="B471" s="53"/>
       <c r="C471" s="168" t="n">
@@ -37832,7 +37832,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="472" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="472" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A472" s="53"/>
       <c r="B472" s="53"/>
       <c r="C472" s="168" t="n">
@@ -37906,7 +37906,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="473" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="473" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A473" s="53"/>
       <c r="B473" s="53"/>
       <c r="C473" s="168" t="n">
@@ -37980,7 +37980,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="474" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="474" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A474" s="53"/>
       <c r="B474" s="53"/>
       <c r="C474" s="168" t="n">
@@ -38054,7 +38054,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="475" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="475" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A475" s="53"/>
       <c r="B475" s="53"/>
       <c r="C475" s="168" t="n">
@@ -38128,7 +38128,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="476" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="476" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A476" s="53"/>
       <c r="B476" s="53"/>
       <c r="C476" s="168" t="n">
@@ -38202,7 +38202,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="477" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="477" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A477" s="53"/>
       <c r="B477" s="53"/>
       <c r="C477" s="175" t="n">
@@ -38276,7 +38276,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="478" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="478" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A478" s="53"/>
       <c r="B478" s="53"/>
       <c r="C478" s="175" t="n">
@@ -38350,7 +38350,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="479" customFormat="false" ht="22.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="479" customFormat="false" ht="22.5" hidden="true" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A479" s="53"/>
       <c r="B479" s="53"/>
       <c r="C479" s="175" t="n">
@@ -38424,7 +38424,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="480" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="480" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A480" s="53"/>
       <c r="B480" s="53"/>
       <c r="C480" s="123" t="n">
@@ -38498,7 +38498,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="481" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="481" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A481" s="53"/>
       <c r="B481" s="53"/>
       <c r="C481" s="123" t="n">
@@ -38572,7 +38572,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="482" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="482" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A482" s="53"/>
       <c r="B482" s="53"/>
       <c r="C482" s="123" t="n">
@@ -38646,7 +38646,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="483" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="483" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A483" s="53"/>
       <c r="B483" s="53"/>
       <c r="C483" s="123" t="n">
@@ -38720,7 +38720,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="484" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="484" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A484" s="53"/>
       <c r="B484" s="53"/>
       <c r="C484" s="123" t="n">
@@ -38794,7 +38794,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="485" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="485" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A485" s="53"/>
       <c r="B485" s="53"/>
       <c r="C485" s="123" t="n">
@@ -38868,7 +38868,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="486" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="486" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A486" s="53"/>
       <c r="B486" s="53"/>
       <c r="C486" s="123" t="n">
@@ -38942,7 +38942,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="487" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="487" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A487" s="53"/>
       <c r="B487" s="53"/>
       <c r="C487" s="123" t="n">
@@ -39016,7 +39016,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="488" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="488" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A488" s="53"/>
       <c r="B488" s="53"/>
       <c r="C488" s="123" t="n">
@@ -39089,7 +39089,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="489" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="489" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A489" s="53"/>
       <c r="B489" s="53"/>
       <c r="C489" s="123" t="n">
@@ -39163,7 +39163,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="490" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="490" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A490" s="53"/>
       <c r="B490" s="53"/>
       <c r="C490" s="123" t="n">
@@ -39237,7 +39237,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="491" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="491" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A491" s="53"/>
       <c r="B491" s="53"/>
       <c r="C491" s="123" t="n">
@@ -39310,7 +39310,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="492" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="492" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A492" s="53"/>
       <c r="B492" s="53"/>
       <c r="C492" s="73" t="n">
@@ -39384,7 +39384,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="493" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="493" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A493" s="53"/>
       <c r="B493" s="53"/>
       <c r="C493" s="73" t="n">
@@ -39458,7 +39458,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="494" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="494" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A494" s="53"/>
       <c r="B494" s="53"/>
       <c r="C494" s="73" t="n">
@@ -39532,7 +39532,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="495" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="495" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A495" s="53"/>
       <c r="B495" s="53"/>
       <c r="C495" s="73" t="n">
@@ -39606,7 +39606,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="496" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="496" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A496" s="53"/>
       <c r="B496" s="53"/>
       <c r="C496" s="73" t="n">
@@ -39680,7 +39680,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="497" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="497" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A497" s="53"/>
       <c r="B497" s="53"/>
       <c r="C497" s="73" t="n">
@@ -39754,7 +39754,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="498" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="498" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A498" s="53"/>
       <c r="B498" s="53"/>
       <c r="C498" s="73" t="n">
@@ -39828,7 +39828,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="499" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="499" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A499" s="53"/>
       <c r="B499" s="53"/>
       <c r="C499" s="73" t="n">
@@ -39902,7 +39902,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="500" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="500" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A500" s="53"/>
       <c r="B500" s="53"/>
       <c r="C500" s="73" t="n">
@@ -39976,7 +39976,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="501" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="501" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A501" s="53"/>
       <c r="B501" s="53"/>
       <c r="C501" s="73" t="n">
@@ -40050,7 +40050,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="502" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="502" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A502" s="53"/>
       <c r="B502" s="53"/>
       <c r="C502" s="73" t="n">
@@ -40124,7 +40124,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="503" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="503" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A503" s="53"/>
       <c r="B503" s="53"/>
       <c r="C503" s="73" t="n">
@@ -40198,7 +40198,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="504" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="504" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A504" s="53"/>
       <c r="B504" s="53"/>
       <c r="C504" s="73" t="n">
@@ -40272,7 +40272,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="505" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="505" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A505" s="53"/>
       <c r="B505" s="53"/>
       <c r="C505" s="73" t="n">
@@ -40346,7 +40346,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="506" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="506" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A506" s="53"/>
       <c r="B506" s="53"/>
       <c r="C506" s="73" t="n">
@@ -40420,7 +40420,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="507" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="507" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A507" s="53"/>
       <c r="B507" s="53"/>
       <c r="C507" s="73" t="n">
@@ -40494,7 +40494,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="508" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="508" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A508" s="53"/>
       <c r="B508" s="53"/>
       <c r="C508" s="73" t="n">
@@ -40568,7 +40568,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="509" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="509" customFormat="false" ht="13.5" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A509" s="53"/>
       <c r="B509" s="53"/>
       <c r="C509" s="73" t="n">
@@ -40642,7 +40642,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="510" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="510" customFormat="false" ht="12" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K510" s="184" t="str">
         <f aca="false">IFERROR(VLOOKUP($J510,$J$10:$K$13,2,0),"")</f>
         <v/>
@@ -40672,7 +40672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="511" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="511" customFormat="false" ht="12" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K511" s="184" t="str">
         <f aca="false">IFERROR(VLOOKUP($J511,$J$10:$K$13,2,0),"")</f>
         <v/>
@@ -40702,7 +40702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="512" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="512" customFormat="false" ht="12" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K512" s="184" t="str">
         <f aca="false">IFERROR(VLOOKUP($J512,$J$10:$K$13,2,0),"")</f>
         <v/>
@@ -40732,7 +40732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="513" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="513" customFormat="false" ht="12" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K513" s="184" t="str">
         <f aca="false">IFERROR(VLOOKUP($J513,$J$10:$K$13,2,0),"")</f>
         <v/>
@@ -40762,7 +40762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="514" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="514" customFormat="false" ht="12" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K514" s="184" t="str">
         <f aca="false">IFERROR(VLOOKUP($J514,$J$10:$K$13,2,0),"")</f>
         <v/>
@@ -40792,7 +40792,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="515" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="515" customFormat="false" ht="12" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K515" s="184" t="str">
         <f aca="false">IFERROR(VLOOKUP($J515,$J$10:$K$13,2,0),"")</f>
         <v/>
@@ -40822,7 +40822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="516" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="516" customFormat="false" ht="12" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K516" s="184" t="str">
         <f aca="false">IFERROR(VLOOKUP($J516,$J$10:$K$13,2,0),"")</f>
         <v/>
@@ -40852,7 +40852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="517" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="517" customFormat="false" ht="12" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K517" s="184" t="str">
         <f aca="false">IFERROR(VLOOKUP($J517,$J$10:$K$13,2,0),"")</f>
         <v/>
@@ -40882,7 +40882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="518" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="518" customFormat="false" ht="12" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K518" s="184" t="str">
         <f aca="false">IFERROR(VLOOKUP($J518,$J$10:$K$13,2,0),"")</f>
         <v/>
@@ -40912,7 +40912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="519" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="519" customFormat="false" ht="12" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K519" s="184" t="str">
         <f aca="false">IFERROR(VLOOKUP($J519,$J$10:$K$13,2,0),"")</f>
         <v/>
@@ -40942,7 +40942,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="520" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="520" customFormat="false" ht="12" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K520" s="184" t="str">
         <f aca="false">IFERROR(VLOOKUP($J520,$J$10:$K$13,2,0),"")</f>
         <v/>
@@ -40972,7 +40972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="521" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="521" customFormat="false" ht="12" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K521" s="184" t="str">
         <f aca="false">IFERROR(VLOOKUP($J521,$J$10:$K$13,2,0),"")</f>
         <v/>
@@ -41002,7 +41002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="522" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="522" customFormat="false" ht="12" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K522" s="184" t="str">
         <f aca="false">IFERROR(VLOOKUP($J522,$J$10:$K$13,2,0),"")</f>
         <v/>
@@ -41032,7 +41032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="523" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="523" customFormat="false" ht="12" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K523" s="184" t="str">
         <f aca="false">IFERROR(VLOOKUP($J523,$J$10:$K$13,2,0),"")</f>
         <v/>
@@ -41062,7 +41062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="524" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="524" customFormat="false" ht="12" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K524" s="184" t="str">
         <f aca="false">IFERROR(VLOOKUP($J524,$J$10:$K$13,2,0),"")</f>
         <v/>
@@ -41092,7 +41092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="525" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="525" customFormat="false" ht="12" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K525" s="184" t="str">
         <f aca="false">IFERROR(VLOOKUP($J525,$J$10:$K$13,2,0),"")</f>
         <v/>
@@ -41122,7 +41122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="526" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="526" customFormat="false" ht="12" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K526" s="184" t="str">
         <f aca="false">IFERROR(VLOOKUP($J526,$J$10:$K$13,2,0),"")</f>
         <v/>
@@ -41152,7 +41152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="527" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="527" customFormat="false" ht="12" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K527" s="184" t="str">
         <f aca="false">IFERROR(VLOOKUP($J527,$J$10:$K$13,2,0),"")</f>
         <v/>
@@ -41182,7 +41182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="528" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="528" customFormat="false" ht="12" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K528" s="184" t="str">
         <f aca="false">IFERROR(VLOOKUP($J528,$J$10:$K$13,2,0),"")</f>
         <v/>
@@ -41212,7 +41212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="529" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="529" customFormat="false" ht="12" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K529" s="184" t="str">
         <f aca="false">IFERROR(VLOOKUP($J529,$J$10:$K$13,2,0),"")</f>
         <v/>
@@ -41242,7 +41242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="530" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="530" customFormat="false" ht="12" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K530" s="184" t="str">
         <f aca="false">IFERROR(VLOOKUP($J530,$J$10:$K$13,2,0),"")</f>
         <v/>
@@ -41272,7 +41272,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="531" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="531" customFormat="false" ht="12" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K531" s="184" t="str">
         <f aca="false">IFERROR(VLOOKUP($J531,$J$10:$K$13,2,0),"")</f>
         <v/>
@@ -41302,7 +41302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="532" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="532" customFormat="false" ht="12" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K532" s="184" t="str">
         <f aca="false">IFERROR(VLOOKUP($J532,$J$10:$K$13,2,0),"")</f>
         <v/>
@@ -41332,7 +41332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="533" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="533" customFormat="false" ht="12" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K533" s="184" t="str">
         <f aca="false">IFERROR(VLOOKUP($J533,$J$10:$K$13,2,0),"")</f>
         <v/>
@@ -41362,7 +41362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="534" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="534" customFormat="false" ht="12" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K534" s="184" t="str">
         <f aca="false">IFERROR(VLOOKUP($J534,$J$10:$K$13,2,0),"")</f>
         <v/>
@@ -41392,7 +41392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="535" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="535" customFormat="false" ht="12" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K535" s="184" t="str">
         <f aca="false">IFERROR(VLOOKUP($J535,$J$10:$K$13,2,0),"")</f>
         <v/>
@@ -41422,7 +41422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="536" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="536" customFormat="false" ht="12" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K536" s="184" t="str">
         <f aca="false">IFERROR(VLOOKUP($J536,$J$10:$K$13,2,0),"")</f>
         <v/>
@@ -41452,7 +41452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="537" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="537" customFormat="false" ht="12" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K537" s="184" t="str">
         <f aca="false">IFERROR(VLOOKUP($J537,$J$10:$K$13,2,0),"")</f>
         <v/>
@@ -41482,7 +41482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="538" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="538" customFormat="false" ht="12" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K538" s="184" t="str">
         <f aca="false">IFERROR(VLOOKUP($J538,$J$10:$K$13,2,0),"")</f>
         <v/>
@@ -41512,7 +41512,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="539" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="539" customFormat="false" ht="12" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K539" s="184" t="str">
         <f aca="false">IFERROR(VLOOKUP($J539,$J$10:$K$13,2,0),"")</f>
         <v/>
@@ -41542,7 +41542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="540" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="540" customFormat="false" ht="12" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K540" s="184" t="str">
         <f aca="false">IFERROR(VLOOKUP($J540,$J$10:$K$13,2,0),"")</f>
         <v/>
@@ -41572,7 +41572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="541" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="541" customFormat="false" ht="12" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K541" s="184" t="str">
         <f aca="false">IFERROR(VLOOKUP($J541,$J$10:$K$13,2,0),"")</f>
         <v/>
@@ -41602,7 +41602,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="542" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="542" customFormat="false" ht="12" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K542" s="184" t="str">
         <f aca="false">IFERROR(VLOOKUP($J542,$J$10:$K$13,2,0),"")</f>
         <v/>
@@ -41632,7 +41632,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="543" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="543" customFormat="false" ht="12" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K543" s="184" t="str">
         <f aca="false">IFERROR(VLOOKUP($J543,$J$10:$K$13,2,0),"")</f>
         <v/>
@@ -41662,7 +41662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="544" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="544" customFormat="false" ht="12" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="K544" s="184" t="str">
         <f aca="false">IFERROR(VLOOKUP($J544,$J$10:$K$13,2,0),"")</f>
         <v/>
@@ -41693,7 +41693,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A18:BB544"/>
+  <autoFilter ref="A18:BB544">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="859293"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <mergeCells count="3">
     <mergeCell ref="AB17:AC17"/>
     <mergeCell ref="AD17:AH17"/>
